--- a/supplies/123975507-1.xlsx
+++ b/supplies/123975507-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>

--- a/supplies/123975507-1.xlsx
+++ b/supplies/123975507-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>

--- a/supplies/123975507-1.xlsx
+++ b/supplies/123975507-1.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
